--- a/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
+++ b/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
@@ -784,12 +784,12 @@
           <t>FAIL</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_06</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>2026-08-29 20:36:59 | Cancel/Reset button failed to respond</t>
         </is>
@@ -832,7 +832,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -842,7 +842,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_POS_07</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-29 20:38:07 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
         </is>
       </c>
     </row>

--- a/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
+++ b/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 20:34:27</t>
+          <t>2026-08-29 21:02:58</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:35:33 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:03:10</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 20:35:59 | Vendor 'Acme Corp' not found in vendor management list</t>
+          <t>2026-08-29 21:03:18</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 20:36:59 | Cancel/Reset button failed to respond</t>
+          <t>2026-08-29 21:03:22</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_07</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-29 20:38:07 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:03:33</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -907,7 +907,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_POS_08</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:03:44</t>
         </is>
       </c>
     </row>
@@ -948,7 +958,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -958,7 +968,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_POS_09</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:03:49</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1021,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1011,7 +1031,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_POS_10</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:03:59</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1084,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>To Be Automated</t>
+          <t>Automated</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1064,7 +1094,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not Executed</t>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_POS_11</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-29 21:04:10</t>
         </is>
       </c>
     </row>
@@ -12174,7 +12214,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
@@ -12184,7 +12224,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:19:51 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:04:34</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12276,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -12246,7 +12286,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:20:58 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:04:47</t>
         </is>
       </c>
     </row>
@@ -12298,7 +12338,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -12308,7 +12348,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:22:07 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:05:00</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12398,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
@@ -12368,7 +12408,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:23:14 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:05:12</t>
         </is>
       </c>
     </row>
@@ -12421,7 +12461,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
@@ -12431,7 +12471,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:24:21 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:05:26</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12524,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -12494,7 +12534,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:25:27 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:05:38</t>
         </is>
       </c>
     </row>
@@ -12552,7 +12592,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 20:25:28</t>
+          <t>2026-08-29 21:05:40</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12644,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
@@ -12614,7 +12654,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:26:37 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:05:53</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
@@ -12679,7 +12719,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:27:51 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:06:06</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12774,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J11" s="0" t="inlineStr">
@@ -12744,7 +12784,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:29:09 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:06:19</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12836,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
@@ -12806,7 +12846,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:29:43 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:06:23</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12898,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J13" s="0" t="inlineStr">
@@ -12868,7 +12908,7 @@
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:30:49 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:06:29</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12961,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
@@ -12931,7 +12971,7 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:32:00 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:06:42</t>
         </is>
       </c>
     </row>
@@ -12984,7 +13024,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
@@ -12994,7 +13034,7 @@
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:33:06 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:06:55</t>
         </is>
       </c>
     </row>
@@ -13046,7 +13086,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="J16" s="0" t="inlineStr">
@@ -13056,7 +13096,7 @@
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-29 20:34:15 | Locator.wait_for: Timeout 8000ms exceeded. Call log:   - waiting for locator("button:has-text('Save'), button:has-text('Submit'), button[type='submit'], button.btn-save").first to be visible </t>
+          <t>2026-08-29 21:07:07</t>
         </is>
       </c>
     </row>

--- a/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
+++ b/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:02:58</t>
+          <t>2026-08-29 21:12:18</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:03:10</t>
+          <t>2026-08-29 21:12:22</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:03:18</t>
+          <t>2026-08-29 21:12:30</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:03:22</t>
+          <t>2026-08-29 21:12:34</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:03:33</t>
+          <t>2026-08-29 21:12:44</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:03:44</t>
+          <t>2026-08-29 21:12:47</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:03:49</t>
+          <t>2026-08-29 21:12:51</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:03:59</t>
+          <t>2026-08-29 21:12:54</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:04:10</t>
+          <t>2026-08-29 21:12:58</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:04:34</t>
+          <t>2026-08-29 21:11:16</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:04:47</t>
+          <t>2026-08-29 21:11:21</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:05:00</t>
+          <t>2026-08-29 21:11:25</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:05:12</t>
+          <t>2026-08-29 21:11:28</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:05:26</t>
+          <t>2026-08-29 21:11:32</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:05:38</t>
+          <t>2026-08-29 21:11:35</t>
         </is>
       </c>
     </row>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:05:40</t>
+          <t>2026-08-29 21:11:38</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:05:53</t>
+          <t>2026-08-29 21:11:42</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:06:06</t>
+          <t>2026-08-29 21:11:47</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:06:19</t>
+          <t>2026-08-29 21:11:51</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:06:23</t>
+          <t>2026-08-29 21:11:54</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:06:29</t>
+          <t>2026-08-29 21:12:00</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:06:42</t>
+          <t>2026-08-29 21:12:06</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:06:55</t>
+          <t>2026-08-29 21:12:11</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13096,7 @@
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:07:07</t>
+          <t>2026-08-29 21:12:15</t>
         </is>
       </c>
     </row>

--- a/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
+++ b/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:18</t>
+          <t>2026-08-30 09:06:03</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:22</t>
+          <t>2026-08-30 09:06:09</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:30</t>
+          <t>2026-08-30 09:06:14</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:34</t>
+          <t>2026-08-30 09:06:17</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:44</t>
+          <t>2026-08-30 09:06:23</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:47</t>
+          <t>2026-08-30 09:06:32</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:51</t>
+          <t>2026-08-30 09:06:36</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:54</t>
+          <t>2026-08-30 09:06:45</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:58</t>
+          <t>2026-08-30 09:06:53</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:16</t>
+          <t>2026-08-30 09:28:20</t>
         </is>
       </c>
     </row>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:21</t>
+          <t>2026-08-30 09:28:32</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:25</t>
+          <t>2026-08-30 09:28:43</t>
         </is>
       </c>
     </row>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:28</t>
+          <t>2026-08-30 09:28:54</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:32</t>
+          <t>2026-08-30 09:29:05</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:35</t>
+          <t>2026-08-30 09:29:15</t>
         </is>
       </c>
     </row>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:38</t>
+          <t>2026-08-30 09:29:17</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:42</t>
+          <t>2026-08-30 09:29:30</t>
         </is>
       </c>
     </row>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:47</t>
+          <t>2026-08-30 09:29:41</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:51</t>
+          <t>2026-08-30 09:29:53</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:11:54</t>
+          <t>2026-08-30 09:29:57</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:00</t>
+          <t>2026-08-30 09:30:03</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:06</t>
+          <t>2026-08-30 09:30:18</t>
         </is>
       </c>
     </row>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:11</t>
+          <t>2026-08-30 09:30:29</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13096,7 @@
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>2026-08-29 21:12:15</t>
+          <t>2026-08-30 09:30:45</t>
         </is>
       </c>
     </row>

--- a/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
+++ b/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1006"/>
+  <dimension ref="A1:K1008"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.88" customWidth="1" style="4" min="1" max="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:06:03</t>
+          <t>2026-09-04 15:47:21</t>
         </is>
       </c>
     </row>
@@ -670,39 +670,45 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:06:09</t>
+          <t>2026-09-04 15:19:41</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TC_VENDOR_POS_04</t>
+          <t>TC_VENDOR_POS_03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Validate new vendor is listed in Vendor Management page via search</t>
+          <t>Verify vendor creation save and confirmation popup</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>New vendor 'Acme Corp' has been created</t>
+          <t>User is on the 'Create Vendor' page with mandatory fields filled</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Vendor Management page\n2. Enter 'Acme Corp' in the search bar\n3. Click 'Search' or press Enter</t>
+          <t>1. Click 'Save'\n2. Click 'Yes' on the confirmation pop-up</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Search Term: 'Acme Corp'</t>
+          <t>Vendor Name: 'Acme Corp'
+Country: 'India'
+Email: 'contact@acmecorp.com'
+Phone: '+91-9876543210'
+Address: '123 Tech Park'
+Active: Ticked
+Payment Terms (Days): 30</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The newly created vendor 'Acme Corp' is listed in the Vendor Management page.</t>
+          <t>Confirmation snackbar is displayed and new vendor is created successfully.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -722,32 +728,154 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>AUT_VENDOR_POS_04</t>
+          <t>AUT_VENDOR_POS_03</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:06:14</t>
+          <t>2026-09-04 15:19:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>TC_VENDOR_POS_04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Validate new vendor is listed in Vendor Management page via search</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>New vendor 'Acme Corp' has been created</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Vendor Management page\n2. Enter 'Acme Corp' in the search bar\n3. Click 'Search' or press Enter</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Search Term: 'Acme Corp'</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The newly created vendor 'Acme Corp' is listed in the Vendor Management page.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_POS_04</t>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_VENDOR_POS_05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Verify successful vendor creation with confirmation pop-up</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and is on the 'Create Vendor' page.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Finance &gt; Vendor Management.
+2. Click 'New Vendor'.
+3. Fill all the input fields.
+4. Click 'Save'.
+5. Click 'Yes' on the confirmation pop-up.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Vendor Name: 'Maple Leaf Traders'
+Country: 'Canada'
+Email: 'contact@mapleleaf.ca'
+Phone: '+1-234-5678'
+Active: Ticked</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation snackbar is displayed and new vendor is created successfully.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_POS_05</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>TC_VENDOR_POS_06</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Verify cancel button functionality during vendor creation</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Finance &gt; Vendor Management.
 2. Click 'New Vendor'.
@@ -755,7 +883,7 @@
 4. Click 'Cancel'.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Britannia Goods Ltd'
 Country: 'UK'
@@ -764,59 +892,59 @@
 Active: Ticked</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>User is returned back to the vendor management page without creating a new vendor.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_06</t>
         </is>
       </c>
-      <c r="K5" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:06:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_POS_07</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Verify successful vendor creation with 'Active' button unticked and optional fields</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Vendor Management.\n2. Click 'New Vendor'.\n3. Fill mandatory fields.\n4. Fill optional fields.\n5. Untick the 'Active' button.\n6. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Dormant Solutions'
 Country: 'USA'
@@ -825,54 +953,54 @@
 Active: Unticked</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>UI: Success message displayed.</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J6" s="0" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_07</t>
         </is>
       </c>
-      <c r="K6" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_POS_08</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Verify selecting 'No' in confirmation pop-up returns to create page</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Finance &gt; Vendor Management.
 2. Click 'New Vendor'.
@@ -881,7 +1009,7 @@
 5. Click 'No' on the confirmation pop-up.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Cancelled Vendor'
 Country: 'Australia'
@@ -890,54 +1018,54 @@
 Active: Ticked</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>User returns to the create page without creating a new vendor.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_08</t>
         </is>
       </c>
-      <c r="K7" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:06:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:20:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_POS_09</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Verify new inactive vendor is created and listed on the vendor management page by searching with include inactive vendor ticked</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Verify new inactive vendor is created and listed on the employee management page by searching with include inactive vendor ticked</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>New inactive vendor has been created.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to employee management page.
 2. Tick the 'Include Inactive' vendor checkbox.
@@ -945,60 +1073,60 @@
 4. Click 'Search' or press Enter.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Search Term: 'Dormant Solutions'
 Include Inactive: Ticked</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>The newly created inactive vendor is listed on the employee management page.</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_09</t>
         </is>
       </c>
-      <c r="K8" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:06:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:20:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_POS_10</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Verify creation with exactly maximum allowed characters in all text fields</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>1. Fill Vendor Name with exactly 100 characters.
 2. Fill other mandatory fields.
@@ -1006,7 +1134,7 @@
 4. Click 'Yes' on confirmation.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'A' (100 times)
 Country: 'USA'
@@ -1014,54 +1142,54 @@
 Phone: '+1-555-000-0000'</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Vendor is created successfully.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_10</t>
         </is>
       </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:06:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:20:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_POS_11</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Verify leading and trailing whitespaces are trimmed from input fields upon saving</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1. Enter Vendor Name with leading and trailing spaces.
 2. Fill other mandatory fields.
@@ -1069,7 +1197,7 @@
 4. Click 'Yes' on confirmation.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: '   Space Corp   '
 Country: 'UK'
@@ -1077,58 +1205,36 @@
 Phone: '+44-555-111-1111'</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Vendor is created successfully and name is saved as 'Space Corp' without spaces.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_POS_11</t>
         </is>
       </c>
-      <c r="K10" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:06:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:20:21</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -12063,6 +12169,28 @@
       <c r="G1006" s="2" t="n"/>
       <c r="H1006" s="2" t="n"/>
       <c r="I1006" s="2" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="n"/>
+      <c r="B1007" s="2" t="n"/>
+      <c r="C1007" s="2" t="n"/>
+      <c r="D1007" s="2" t="n"/>
+      <c r="E1007" s="2" t="n"/>
+      <c r="F1007" s="2" t="n"/>
+      <c r="G1007" s="2" t="n"/>
+      <c r="H1007" s="2" t="n"/>
+      <c r="I1007" s="2" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="n"/>
+      <c r="B1008" s="2" t="n"/>
+      <c r="C1008" s="2" t="n"/>
+      <c r="D1008" s="2" t="n"/>
+      <c r="E1008" s="2" t="n"/>
+      <c r="F1008" s="2" t="n"/>
+      <c r="G1008" s="2" t="n"/>
+      <c r="H1008" s="2" t="n"/>
+      <c r="I1008" s="2" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I1008">
@@ -12095,7 +12223,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="20.38" customWidth="1" style="4" min="1" max="1"/>
@@ -12224,7 +12352,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:28:20</t>
+          <t>2026-09-04 15:17:29</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12404,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
@@ -12286,7 +12414,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:28:32</t>
+          <t>2026-09-04 15:17:37 | Application defect: Application accepted duplicate email address without returning conflict error (redirected to vendor details page)</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12466,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
@@ -12348,7 +12476,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:28:43</t>
+          <t>2026-09-04 15:17:41 | Application defect: Application accepted raw SQL injection payload without input rejection or sanitation (redirected to vendor details page)</t>
         </is>
       </c>
     </row>
@@ -12398,7 +12526,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
@@ -12408,7 +12536,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:28:54</t>
+          <t>2026-09-04 15:17:44 | Application defect: Application accepted Vendor Name exceeding 100 character maximum limit (redirected to vendor details page)</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12599,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:29:05</t>
+          <t>2026-09-04 15:18:02</t>
         </is>
       </c>
     </row>
@@ -12534,92 +12662,157 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>2026-08-30 09:29:15</t>
+          <t>2026-09-04 15:18:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>TC_VENDOR_NEG_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Verify vendor is not created when clicking 'No' on the confirmation pop-up</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and is on the 'Create Vendor' page.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Finance &gt; Vendor Management.
+2. Click 'New Vendor'.
+3. Fill all the input fields.
+4. Click 'Save'.
+5. Click 'No' (or dismiss) on the confirmation pop-up.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Vendor Name: 'No Confirm Vendor'
+Country: 'Australia'
+Email: 'noconfirm@vendor.com'
+Phone: '+61-123-4567'
+Active: Ticked</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Pop-up is closed. User remains on the 'Create Vendor' page and vendor is not created.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_NEG_07</t>
+        </is>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>TC_VENDOR_NEG_08</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Verify navigation fails if user is not logged in as Admin</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>User is logged in as a non-Admin user</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Finance
 2. Attempt to click on Vendor Management icon</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Vendor Management icon is not visible or access is denied.</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J8" s="0" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_08</t>
         </is>
       </c>
-      <c r="K8" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:29:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:30 | Application defect: Non-admin user was granted unauthorized access to Vendor Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_09</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Attempt to create vendor with existing duplicate Vendor Name</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin. A vendor with name 'Acme Corp' exists.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Vendor'
 2. Enter existing Vendor Name
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Acme Corp'
 Country: 'USA'
@@ -12627,61 +12820,61 @@
 Phone: '+1-800-555-0199'</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>UI: Error message 'Vendor Name already exists' displayed.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J9" s="0" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_09</t>
         </is>
       </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:29:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:36 | Application defect: Application accepted duplicate Vendor Name without validation error (redirected to vendor details page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_10</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Attempt to create vendor with non-alphabetic characters in Name, Address, State, and POC</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on Vendor Management page.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Vendor'
 2. Enter numeric/special characters in Vendor Name, Address, State, and POC
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Acme123!'
 Country: 'USA'
@@ -12692,61 +12885,61 @@
 Phone: '+1-800-555-0199'</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>UI: Validation errors displayed for non-alphabetic input.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_10</t>
         </is>
       </c>
-      <c r="K10" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:29:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:39 | Application defect: Application accepted numeric/special characters in name/address/state/POC fields (redirected to vendor details page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_11</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Attempt to create vendor with non-numeric characters in Tax Number, Phone, Percentage, and Days</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on Vendor Management page.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1. Click 'New Vendor'
 2. Enter alphabetic/special characters in Tax Number, Phone, Percentage, and Days
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Non Numeric Vendor'
 Country: 'USA'
@@ -12757,61 +12950,123 @@
 Days: 'Five'</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>UI: Validation errors displayed for non-numeric input.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J11" s="0" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_11</t>
         </is>
       </c>
-      <c r="K11" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:29:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:43 | Application defect: Application accepted non-numeric characters in numeric fields (tax/phone/percentage/days) (redirected to vendor details page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC_VENDOR_NEG_12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Attempt to create vendor with improper email format</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and is on Vendor Management page.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'New Vendor'
+2. Enter invalid email format
+3. Click 'Save'</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Vendor Name: 'Improper Email Vendor'
+Country: 'Germany'
+Email: 'invalid.email@com'
+Phone: '+49-123-456789'</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>UI: Validation error 'Invalid email format' displayed.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_NEG_12</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:46 | Application defect: Application accepted improper email format without validation error (redirected to vendor details page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_13</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Attempt to create vendor after session timeout exceeds</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin and is on Create Vendor page.</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>1. Fill vendor details
 2. Wait for session to timeout
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Timeout Vendor'
 Country: 'France'
@@ -12819,61 +13074,61 @@
 Phone: '+33-123-456-789'</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>UI: User is redirected to login page with timeout message.</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J12" s="0" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_13</t>
         </is>
       </c>
-      <c r="K12" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:29:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_14</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Attempt to create vendor when network is idle or server is down</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>User is logged in as Admin, on Create Vendor page, and network is disconnected/server is down.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>1. Fill vendor details
 2. Disconnect network/simulate server down
 3. Click 'Save'</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Network Idle Vendor'
 Country: 'Spain'
@@ -12881,61 +13136,123 @@
 Phone: '+34-123-456-789'</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>UI: Network error or Server unreachable message displayed.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J13" s="0" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_14</t>
         </is>
       </c>
-      <c r="K13" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:30:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC_VENDOR_NEG_15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Validate that a vendor creation failed due to session timeout is not listed on the Vendor Management page</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Vendor creation failed due to session timeout.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in again
+2. Navigate to Vendor Management page
+3. Search for the vendor</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Vendor Name: 'Timeout Vendor'
+Country: 'France'
+Email: 'timeout@example.com'
+Phone: '+33-123-456-789'</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Vendor is not displayed in the list.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>AUT_VENDOR_NEG_15</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_16</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Attempt to create a vendor with Percentage field &gt; 100% or &lt; 0%</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>1. Enter valid mandatory fields.
 2. Enter '105' in Percentage field.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Percent Test'
 Country: 'USA'
@@ -12944,61 +13261,61 @@
 Percentage: 105</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Error message displayed indicating percentage must be between 0 and 100. Vendor is not created.</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="J14" s="0" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_16</t>
         </is>
       </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:30:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_17</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Attempt to create a vendor with negative Payment Terms (Days)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1. Enter valid mandatory fields.
 2. Enter '-5' in Payment Terms.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: 'Payment Test'
 Country: 'USA'
@@ -13007,61 +13324,61 @@
 Payment Terms (Days): -5</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Error message displayed indicating payment terms cannot be negative. Vendor is not created.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J15" s="0" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_17</t>
         </is>
       </c>
-      <c r="K15" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:30:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:31 | Application defect: Application accepted negative Payment Terms (Days) value (redirected to vendor details page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>TC_VENDOR_NEG_18</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Attempt to create a vendor with an XSS payload in the Name field</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>User is on the 'Create Vendor' page.</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>1. Enter XSS payload in Vendor Name.
 2. Fill other mandatory fields.
 3. Click 'Save'.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Vendor Name: '&lt;script&gt;alert("XSS")&lt;/script&gt;'
 Country: 'USA'
@@ -13069,34 +13386,34 @@
 Phone: '+1-555-444-4444'</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>System sanitizes the input or rejects it with an error. No script is executed.</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>UI</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J16" s="0" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>AUT_VENDOR_NEG_18</t>
         </is>
       </c>
-      <c r="K16" s="0" t="inlineStr">
-        <is>
-          <t>2026-08-30 09:30:45</t>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04 15:19:35 | Application defect: Application executed raw XSS script tag payload without input sanitation (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>

--- a/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
+++ b/swarajya-create/vendor-management/test_data/Create-Vendor-Management.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:47:21</t>
+          <t>2026-09-07 15:07:09</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:41</t>
+          <t>2026-09-07 15:07:14</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:44</t>
+          <t>2026-09-07 15:07:15</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:48</t>
+          <t>2026-09-07 15:07:18</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:51</t>
+          <t>2026-09-07 15:07:19</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:53</t>
+          <t>2026-09-07 15:07:21</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:56</t>
+          <t>2026-09-07 15:07:22</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:20:12</t>
+          <t>2026-09-07 15:07:36</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:20:15</t>
+          <t>2026-09-07 15:07:38</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:20:18</t>
+          <t>2026-09-07 15:07:39</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:20:21</t>
+          <t>2026-09-07 15:07:41</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:17:29</t>
+          <t>2026-09-07 15:05:38</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:17:37 | Application defect: Application accepted duplicate email address without returning conflict error (redirected to vendor details page)</t>
+          <t>2026-09-07 15:05:45 | Application defect: Application accepted duplicate email address without returning conflict error (redirected to vendor details page)</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:17:41 | Application defect: Application accepted raw SQL injection payload without input rejection or sanitation (redirected to vendor details page)</t>
+          <t>2026-09-07 15:05:47 | Application defect: Application accepted raw SQL injection payload without input rejection or sanitation (redirected to vendor details page)</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:17:44 | Application defect: Application accepted Vendor Name exceeding 100 character maximum limit (redirected to vendor details page)</t>
+          <t>2026-09-07 15:05:48 | Application defect: Application accepted Vendor Name exceeding 100 character maximum limit (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:02</t>
+          <t>2026-09-07 15:06:05</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:21</t>
+          <t>2026-09-07 15:06:23</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:24</t>
+          <t>2026-09-07 15:06:25</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:30 | Application defect: Non-admin user was granted unauthorized access to Vendor Management</t>
+          <t>2026-09-07 15:06:28 | Application defect: Non-admin user was granted unauthorized access to Vendor Management</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:36 | Application defect: Application accepted duplicate Vendor Name without validation error (redirected to vendor details page)</t>
+          <t>2026-09-07 15:06:32 | Application defect: Application accepted duplicate Vendor Name without validation error (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:39 | Application defect: Application accepted numeric/special characters in name/address/state/POC fields (redirected to vendor details page)</t>
+          <t>2026-09-07 15:06:34 | Application defect: Application accepted numeric/special characters in name/address/state/POC fields (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:43 | Application defect: Application accepted non-numeric characters in numeric fields (tax/phone/percentage/days) (redirected to vendor details page)</t>
+          <t>2026-09-07 15:06:35 | Application defect: Application accepted non-numeric characters in numeric fields (tax/phone/percentage/days) (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K13" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:46 | Application defect: Application accepted improper email format without validation error (redirected to vendor details page)</t>
+          <t>2026-09-07 15:06:37 | Application defect: Application accepted improper email format without validation error (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:49</t>
+          <t>2026-09-07 15:06:39</t>
         </is>
       </c>
     </row>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:18:54</t>
+          <t>2026-09-07 15:06:43</t>
         </is>
       </c>
     </row>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="K16" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:01</t>
+          <t>2026-09-07 15:06:48</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="K17" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:28</t>
+          <t>2026-09-07 15:07:05</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="K18" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:31 | Application defect: Application accepted negative Payment Terms (Days) value (redirected to vendor details page)</t>
+          <t>2026-09-07 15:07:07 | Application defect: Application accepted negative Payment Terms (Days) value (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="K19" s="0" t="inlineStr">
         <is>
-          <t>2026-09-04 15:19:35 | Application defect: Application executed raw XSS script tag payload without input sanitation (success toast displayed: 'Vendor Added Successfully!')</t>
+          <t>2026-09-07 15:07:08 | Application defect: Application executed raw XSS script tag payload without input sanitation (success toast displayed: 'Vendor Added Successfully!')</t>
         </is>
       </c>
     </row>
